--- a/Nirav Contractor Excel Task.xlsx
+++ b/Nirav Contractor Excel Task.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BCC74393-77CF-4777-9516-B43320C672F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{49002FB6-C87A-4581-9027-F5E5455948AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="2" activeTab="7" xr2:uid="{BC978020-3D4F-4491-875C-11B5EA85048D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" firstSheet="2" activeTab="10" xr2:uid="{BC978020-3D4F-4491-875C-11B5EA85048D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -44,7 +44,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="421" uniqueCount="204">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="209">
   <si>
     <t>Employee ID</t>
   </si>
@@ -656,6 +656,21 @@
   </si>
   <si>
     <t>Rita</t>
+  </si>
+  <si>
+    <t>Jay</t>
+  </si>
+  <si>
+    <t>Devanshi</t>
+  </si>
+  <si>
+    <t>Jiya</t>
+  </si>
+  <si>
+    <t>Meet</t>
+  </si>
+  <si>
+    <t>Nitya</t>
   </si>
 </sst>
 </file>
@@ -663,7 +678,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="169" formatCode="&quot;₹&quot;\ #,##0.00"/>
+    <numFmt numFmtId="164" formatCode="&quot;₹&quot;\ #,##0.00"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
@@ -833,7 +848,6 @@
   </cellStyleXfs>
   <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -861,20 +875,14 @@
     <xf numFmtId="14" fontId="4" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="169" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="169" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
     </xf>
-    <xf numFmtId="169" fontId="4" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="4" fillId="2" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -918,13 +926,20 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Heading 2" xfId="2" builtinId="17"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="23">
+  <dxfs count="19">
     <dxf>
       <fill>
         <patternFill>
@@ -952,27 +967,6 @@
     <dxf>
       <fill>
         <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
           <bgColor rgb="FF00B050"/>
         </patternFill>
       </fill>
@@ -984,13 +978,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -1015,15 +1002,6 @@
       </fill>
     </dxf>
     <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1040,22 +1018,6 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color rgb="FF1F2328"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
       <fill>
         <patternFill patternType="solid">
           <fgColor indexed="64"/>
@@ -1063,41 +1025,6 @@
         </patternFill>
       </fill>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-      <border diagonalUp="0" diagonalDown="0" outline="0">
-        <left style="medium">
-          <color rgb="FFD1D9E0"/>
-        </left>
-        <right style="medium">
-          <color rgb="FFD1D9E0"/>
-        </right>
-        <top/>
-        <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="12"/>
-        <color rgb="FF1F2328"/>
-        <name val="Segoe UI"/>
-        <family val="2"/>
-        <scheme val="none"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor rgb="FFFFFFFF"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <font>
@@ -1313,6 +1240,66 @@
         </bottom>
       </border>
     </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF1F2328"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="1" indent="1" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="12"/>
+        <color rgb="FF1F2328"/>
+        <name val="Segoe UI"/>
+        <family val="2"/>
+        <scheme val="none"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor rgb="FFFFFFFF"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <border diagonalUp="0" diagonalDown="0" outline="0">
+        <left style="medium">
+          <color rgb="FFD1D9E0"/>
+        </left>
+        <right style="medium">
+          <color rgb="FFD1D9E0"/>
+        </right>
+        <top/>
+        <bottom/>
+      </border>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1327,26 +1314,26 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{339D2F51-B2CE-4794-BD2A-5A3CEED73A37}" name="Table6" displayName="Table6" ref="A2:E24" totalsRowShown="0" headerRowDxfId="15" dataDxfId="16" tableBorderDxfId="22">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{339D2F51-B2CE-4794-BD2A-5A3CEED73A37}" name="Table6" displayName="Table6" ref="A2:E24" totalsRowShown="0" headerRowDxfId="18" dataDxfId="17" tableBorderDxfId="16">
   <autoFilter ref="A2:E24" xr:uid="{339D2F51-B2CE-4794-BD2A-5A3CEED73A37}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{14DEB57B-3427-4C5F-B734-E9BEB2AD966D}" name="Employee ID" dataDxfId="21"/>
-    <tableColumn id="2" xr3:uid="{62FD802E-D282-4898-AD61-3016D975637A}" name="Name" dataDxfId="20"/>
-    <tableColumn id="3" xr3:uid="{351A9D04-C53D-41E5-A8FB-3E66EAC29843}" name="Department" dataDxfId="19"/>
-    <tableColumn id="4" xr3:uid="{BCCFCFB2-5C72-4059-A102-C6AC0902D128}" name="Salary" dataDxfId="18"/>
-    <tableColumn id="5" xr3:uid="{CE2A0571-EC28-4B78-AC16-EE1F5BDAF1D9}" name="Joining Date" dataDxfId="17"/>
+    <tableColumn id="1" xr3:uid="{14DEB57B-3427-4C5F-B734-E9BEB2AD966D}" name="Employee ID" dataDxfId="15"/>
+    <tableColumn id="2" xr3:uid="{62FD802E-D282-4898-AD61-3016D975637A}" name="Name" dataDxfId="14"/>
+    <tableColumn id="3" xr3:uid="{351A9D04-C53D-41E5-A8FB-3E66EAC29843}" name="Department" dataDxfId="13"/>
+    <tableColumn id="4" xr3:uid="{BCCFCFB2-5C72-4059-A102-C6AC0902D128}" name="Salary" dataDxfId="12"/>
+    <tableColumn id="5" xr3:uid="{CE2A0571-EC28-4B78-AC16-EE1F5BDAF1D9}" name="Joining Date" dataDxfId="11"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight9" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{A64C2122-2A92-4DDF-9E53-A4EFC65D05FF}" name="Table10" displayName="Table10" ref="A2:C26" totalsRowShown="0" headerRowDxfId="11" headerRowCellStyle="Heading 2" dataCellStyle="Heading 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="10" xr:uid="{A64C2122-2A92-4DDF-9E53-A4EFC65D05FF}" name="Table10" displayName="Table10" ref="A2:C26" totalsRowShown="0" headerRowDxfId="10" headerRowCellStyle="Heading 2" dataCellStyle="Heading 2">
   <autoFilter ref="A2:C26" xr:uid="{A64C2122-2A92-4DDF-9E53-A4EFC65D05FF}"/>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{07A1D7CC-1AB2-47EE-9C7F-EB166C168A24}" name="Invoice No" dataDxfId="14" dataCellStyle="Heading 2"/>
-    <tableColumn id="2" xr3:uid="{6D5ED51D-B716-45B5-8C90-5AE48D745F41}" name="Date" dataDxfId="13" dataCellStyle="Heading 2"/>
-    <tableColumn id="3" xr3:uid="{3D155910-829B-4D1B-8080-41DC1698D7F6}" name="Sales Amount" dataDxfId="12" dataCellStyle="Heading 2"/>
+    <tableColumn id="1" xr3:uid="{07A1D7CC-1AB2-47EE-9C7F-EB166C168A24}" name="Invoice No" dataDxfId="9" dataCellStyle="Heading 2"/>
+    <tableColumn id="2" xr3:uid="{6D5ED51D-B716-45B5-8C90-5AE48D745F41}" name="Date" dataDxfId="8" dataCellStyle="Heading 2"/>
+    <tableColumn id="3" xr3:uid="{3D155910-829B-4D1B-8080-41DC1698D7F6}" name="Sales Amount" dataDxfId="7" dataCellStyle="Heading 2"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight10" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1673,375 +1660,375 @@
   <sheetData>
     <row r="1" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="5" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="3" t="s">
+      <c r="A3" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D3" s="11">
+      <c r="D3" s="10">
         <v>32000</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E3" s="6">
         <v>44573</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="12">
+      <c r="D4" s="11">
         <v>45000</v>
       </c>
-      <c r="E4" s="8">
+      <c r="E4" s="7">
         <v>44260</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D5" s="11">
+      <c r="D5" s="10">
         <v>38000</v>
       </c>
-      <c r="E5" s="7">
+      <c r="E5" s="6">
         <v>44030</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D6" s="12">
+      <c r="D6" s="11">
         <v>52000</v>
       </c>
-      <c r="E6" s="8">
+      <c r="E6" s="7">
         <v>43779</v>
       </c>
     </row>
     <row r="7" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="9" t="s">
+      <c r="B7" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C7" s="9" t="s">
+      <c r="C7" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="D7" s="13">
+      <c r="D7" s="12">
         <v>30000</v>
       </c>
-      <c r="E7" s="10">
+      <c r="E7" s="9">
         <v>45102</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D8" s="11">
+      <c r="D8" s="10">
         <v>40300</v>
       </c>
-      <c r="E8" s="7">
+      <c r="E8" s="6">
         <v>44573</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D9" s="12">
+      <c r="D9" s="11">
         <v>40600</v>
       </c>
-      <c r="E9" s="8">
+      <c r="E9" s="7">
         <v>44260</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C10" s="3" t="s">
+      <c r="C10" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D10" s="11">
+      <c r="D10" s="10">
         <v>40900</v>
       </c>
-      <c r="E10" s="7">
+      <c r="E10" s="6">
         <v>44030</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D11" s="12">
+      <c r="D11" s="11">
         <v>41200</v>
       </c>
-      <c r="E11" s="8">
+      <c r="E11" s="7">
         <v>43779</v>
       </c>
     </row>
     <row r="12" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B12" s="9" t="s">
+      <c r="B12" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="C12" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="D12" s="13">
+      <c r="D12" s="12">
         <v>41500</v>
       </c>
-      <c r="E12" s="10">
+      <c r="E12" s="9">
         <v>45102</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D13" s="11">
+      <c r="D13" s="10">
         <v>41800</v>
       </c>
-      <c r="E13" s="7">
+      <c r="E13" s="6">
         <v>44573</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="12">
+      <c r="D14" s="11">
         <v>42100</v>
       </c>
-      <c r="E14" s="8">
+      <c r="E14" s="7">
         <v>44260</v>
       </c>
     </row>
     <row r="15" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C15" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D15" s="11">
+      <c r="D15" s="10">
         <v>42400</v>
       </c>
-      <c r="E15" s="7">
+      <c r="E15" s="6">
         <v>44030</v>
       </c>
     </row>
     <row r="16" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D16" s="12">
+      <c r="D16" s="11">
         <v>42700</v>
       </c>
-      <c r="E16" s="8">
+      <c r="E16" s="7">
         <v>43779</v>
       </c>
     </row>
     <row r="17" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="B17" s="9" t="s">
+      <c r="B17" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C17" s="9" t="s">
+      <c r="C17" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="D17" s="13">
+      <c r="D17" s="12">
         <v>43000</v>
       </c>
-      <c r="E17" s="10">
+      <c r="E17" s="9">
         <v>45102</v>
       </c>
     </row>
     <row r="18" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C18" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="D18" s="11">
+      <c r="D18" s="10">
         <v>43300</v>
       </c>
-      <c r="E18" s="7">
+      <c r="E18" s="6">
         <v>44573</v>
       </c>
     </row>
     <row r="19" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D19" s="12">
+      <c r="D19" s="11">
         <v>43600</v>
       </c>
-      <c r="E19" s="8">
+      <c r="E19" s="7">
         <v>44260</v>
       </c>
     </row>
     <row r="20" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C20" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D20" s="11">
+      <c r="D20" s="10">
         <v>43900</v>
       </c>
-      <c r="E20" s="7">
+      <c r="E20" s="6">
         <v>44030</v>
       </c>
     </row>
     <row r="21" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="D21" s="12">
+      <c r="D21" s="11">
         <v>44200</v>
       </c>
-      <c r="E21" s="8">
+      <c r="E21" s="7">
         <v>43779</v>
       </c>
     </row>
     <row r="22" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="B22" s="9" t="s">
+      <c r="B22" s="8" t="s">
         <v>17</v>
       </c>
-      <c r="C22" s="9" t="s">
+      <c r="C22" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="D22" s="13">
+      <c r="D22" s="12">
         <v>44500</v>
       </c>
-      <c r="E22" s="10">
+      <c r="E22" s="9">
         <v>45102</v>
       </c>
     </row>
     <row r="23" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="3"/>
-      <c r="B23" s="3"/>
-      <c r="C23" s="3"/>
-      <c r="D23" s="3"/>
-      <c r="E23" s="7"/>
+      <c r="A23" s="2"/>
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="6"/>
     </row>
     <row r="24" spans="1:5" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="3"/>
-      <c r="B24" s="4"/>
-      <c r="C24" s="3"/>
-      <c r="D24" s="3"/>
-      <c r="E24" s="7"/>
+      <c r="A24" s="2"/>
+      <c r="B24" s="3"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="6"/>
     </row>
   </sheetData>
   <phoneticPr fontId="6" type="noConversion"/>
@@ -2291,14 +2278,14 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="C2:C21">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="lessThan">
+      <formula>40</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="greaterThanOrEqual">
+      <formula>75</formula>
+    </cfRule>
     <cfRule type="cellIs" priority="3" operator="greaterThanOrEqual">
       <formula>75</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="6" priority="2" operator="greaterThanOrEqual">
-      <formula>75</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="7" priority="1" operator="lessThan">
-      <formula>40</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2314,12 +2301,12 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+      <c r="A1" s="31" t="s">
         <v>190</v>
       </c>
-      <c r="B1" s="1"/>
-      <c r="C1" s="1"/>
-      <c r="D1" s="1"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
@@ -2486,15 +2473,15 @@
     <mergeCell ref="A1:D1"/>
   </mergeCells>
   <conditionalFormatting sqref="B3:B21">
-    <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThanOrEqual">
-      <formula>50000</formula>
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
+      <formula>30000</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="1" priority="2" operator="between">
       <formula>30000</formula>
       <formula>49999</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <formula>30000</formula>
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThanOrEqual">
+      <formula>50000</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2512,276 +2499,276 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="23.25" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="29" t="s">
         <v>50</v>
       </c>
-      <c r="B1" s="15"/>
-      <c r="C1" s="15"/>
-      <c r="D1" s="15"/>
+      <c r="B1" s="30"/>
+      <c r="C1" s="30"/>
+      <c r="D1" s="30"/>
     </row>
     <row r="2" spans="1:4" ht="35.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="2" t="s">
+      <c r="A2" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="16" t="s">
+      <c r="A3" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C3" s="11">
+      <c r="C3" s="10">
         <v>45000</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="2" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="17" t="s">
+      <c r="A4" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C4" s="12">
+      <c r="C4" s="11">
         <v>1200</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="3" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="16" t="s">
+      <c r="A5" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C5" s="11">
+      <c r="C5" s="10">
         <v>18000</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="2" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="17" t="s">
+      <c r="A6" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C6" s="12">
+      <c r="C6" s="11">
         <v>62000</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="3" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="16" t="s">
+      <c r="A7" s="13" t="s">
         <v>51</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C7" s="11">
+      <c r="C7" s="10">
         <v>48500</v>
       </c>
-      <c r="D7" s="3" t="s">
+      <c r="D7" s="2" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="17" t="s">
+      <c r="A8" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="11">
         <v>55280</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="3" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="16" t="s">
+      <c r="A9" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C9" s="11">
+      <c r="C9" s="10">
         <v>62060</v>
       </c>
-      <c r="D9" s="3" t="s">
+      <c r="D9" s="2" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="17" t="s">
+      <c r="A10" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C10" s="12">
+      <c r="C10" s="11">
         <v>68840</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="3" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="16" t="s">
+      <c r="A11" s="13" t="s">
         <v>52</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C11" s="11">
+      <c r="C11" s="10">
         <v>75620</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="2" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="12" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="17" t="s">
+      <c r="A12" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C12" s="12">
+      <c r="C12" s="11">
         <v>82400</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="3" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="16" t="s">
+      <c r="A13" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C13" s="11">
+      <c r="C13" s="10">
         <v>89180</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="2" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="14" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="17" t="s">
+      <c r="A14" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C14" s="12">
+      <c r="C14" s="11">
         <v>95960</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="3" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="16" t="s">
+      <c r="A15" s="13" t="s">
         <v>53</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C15" s="11">
+      <c r="C15" s="10">
         <v>102740</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" s="2" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="16" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="17" t="s">
+      <c r="A16" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C16" s="12">
+      <c r="C16" s="11">
         <v>109520</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="3" t="s">
         <v>43</v>
       </c>
     </row>
     <row r="17" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="16" t="s">
+      <c r="A17" s="13" t="s">
         <v>44</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="C17" s="11">
+      <c r="C17" s="10">
         <v>116300</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="D17" s="2" t="s">
         <v>46</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="17" t="s">
+      <c r="A18" s="14" t="s">
         <v>47</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="C18" s="12">
+      <c r="C18" s="11">
         <v>123080</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="3" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="19" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="16" t="s">
+      <c r="A19" s="13" t="s">
         <v>54</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C19" s="11">
+      <c r="C19" s="10">
         <v>129860</v>
       </c>
-      <c r="D19" s="3" t="s">
+      <c r="D19" s="2" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="20" spans="1:4" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="17" t="s">
+      <c r="A20" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="C20" s="12">
+      <c r="C20" s="11">
         <v>136640</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="3" t="s">
         <v>43</v>
       </c>
     </row>
@@ -2796,29 +2783,29 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEBDA245-03AA-418A-980F-65D2C1B48625}">
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="6" max="6" width="11.28515625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="18" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="19" t="s">
+      <c r="A1" s="16" t="s">
         <v>55</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="C1" s="16" t="s">
         <v>56</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="D1" s="16" t="s">
         <v>57</v>
       </c>
-      <c r="E1" s="19" t="s">
+      <c r="E1" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="F1" s="19" t="s">
+      <c r="F1" s="16" t="s">
         <v>59</v>
       </c>
     </row>
@@ -2838,7 +2825,7 @@
       <c r="E2">
         <v>25</v>
       </c>
-      <c r="F2" s="18">
+      <c r="F2" s="15">
         <f>AVERAGE(C2,D2,E2)</f>
         <v>31.666666666666668</v>
       </c>
@@ -2859,8 +2846,8 @@
       <c r="E3">
         <v>86</v>
       </c>
-      <c r="F3" s="18">
-        <f t="shared" ref="F3:F6" si="0">AVERAGE(C3,D3,E3)</f>
+      <c r="F3" s="15">
+        <f t="shared" ref="F3:F21" si="0">AVERAGE(C3,D3,E3)</f>
         <v>61.333333333333336</v>
       </c>
     </row>
@@ -2880,7 +2867,7 @@
       <c r="E4">
         <v>64</v>
       </c>
-      <c r="F4" s="18">
+      <c r="F4" s="15">
         <f t="shared" si="0"/>
         <v>69.333333333333329</v>
       </c>
@@ -2901,7 +2888,7 @@
       <c r="E5">
         <v>55</v>
       </c>
-      <c r="F5" s="18">
+      <c r="F5" s="15">
         <f t="shared" si="0"/>
         <v>42.666666666666664</v>
       </c>
@@ -2922,9 +2909,324 @@
       <c r="E6">
         <v>33</v>
       </c>
-      <c r="F6" s="18">
+      <c r="F6" s="15">
         <f t="shared" si="0"/>
         <v>32.333333333333336</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>62</v>
+      </c>
+      <c r="C7">
+        <v>24</v>
+      </c>
+      <c r="D7">
+        <v>67</v>
+      </c>
+      <c r="E7">
+        <v>56</v>
+      </c>
+      <c r="F7" s="15">
+        <f t="shared" si="0"/>
+        <v>49</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>108</v>
+      </c>
+      <c r="C8">
+        <v>42</v>
+      </c>
+      <c r="D8">
+        <v>74</v>
+      </c>
+      <c r="E8">
+        <v>75</v>
+      </c>
+      <c r="F8" s="15">
+        <f t="shared" si="0"/>
+        <v>63.666666666666664</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>204</v>
+      </c>
+      <c r="C9">
+        <v>35</v>
+      </c>
+      <c r="D9">
+        <v>45</v>
+      </c>
+      <c r="E9">
+        <v>34</v>
+      </c>
+      <c r="F9" s="15">
+        <f t="shared" si="0"/>
+        <v>38</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>179</v>
+      </c>
+      <c r="C10">
+        <v>66</v>
+      </c>
+      <c r="D10">
+        <v>58</v>
+      </c>
+      <c r="E10">
+        <v>55</v>
+      </c>
+      <c r="F10" s="15">
+        <f t="shared" si="0"/>
+        <v>59.666666666666664</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>140</v>
+      </c>
+      <c r="C11">
+        <v>46</v>
+      </c>
+      <c r="D11">
+        <v>62</v>
+      </c>
+      <c r="E11">
+        <v>54</v>
+      </c>
+      <c r="F11" s="15">
+        <f t="shared" si="0"/>
+        <v>54</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>205</v>
+      </c>
+      <c r="C12">
+        <v>57</v>
+      </c>
+      <c r="D12">
+        <v>31</v>
+      </c>
+      <c r="E12">
+        <v>67</v>
+      </c>
+      <c r="F12" s="15">
+        <f t="shared" si="0"/>
+        <v>51.666666666666664</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>107</v>
+      </c>
+      <c r="C13">
+        <v>43</v>
+      </c>
+      <c r="D13">
+        <v>35</v>
+      </c>
+      <c r="E13">
+        <v>22</v>
+      </c>
+      <c r="F13" s="15">
+        <f t="shared" si="0"/>
+        <v>33.333333333333336</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" t="s">
+        <v>206</v>
+      </c>
+      <c r="C14">
+        <v>28</v>
+      </c>
+      <c r="D14">
+        <v>25</v>
+      </c>
+      <c r="E14">
+        <v>59</v>
+      </c>
+      <c r="F14" s="15">
+        <f t="shared" si="0"/>
+        <v>37.333333333333336</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" t="s">
+        <v>207</v>
+      </c>
+      <c r="C15">
+        <v>49</v>
+      </c>
+      <c r="D15">
+        <v>56</v>
+      </c>
+      <c r="E15">
+        <v>34</v>
+      </c>
+      <c r="F15" s="15">
+        <f t="shared" si="0"/>
+        <v>46.333333333333336</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" t="s">
+        <v>203</v>
+      </c>
+      <c r="C16">
+        <v>36</v>
+      </c>
+      <c r="D16">
+        <v>28</v>
+      </c>
+      <c r="E16">
+        <v>47</v>
+      </c>
+      <c r="F16" s="15">
+        <f t="shared" si="0"/>
+        <v>37</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" t="s">
+        <v>61</v>
+      </c>
+      <c r="C17">
+        <v>49</v>
+      </c>
+      <c r="D17">
+        <v>39</v>
+      </c>
+      <c r="E17">
+        <v>25</v>
+      </c>
+      <c r="F17" s="15">
+        <f t="shared" si="0"/>
+        <v>37.666666666666664</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" t="s">
+        <v>188</v>
+      </c>
+      <c r="C18">
+        <v>53</v>
+      </c>
+      <c r="D18">
+        <v>41</v>
+      </c>
+      <c r="E18">
+        <v>33</v>
+      </c>
+      <c r="F18" s="15">
+        <f t="shared" si="0"/>
+        <v>42.333333333333336</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" t="s">
+        <v>104</v>
+      </c>
+      <c r="C19">
+        <v>46</v>
+      </c>
+      <c r="D19">
+        <v>48</v>
+      </c>
+      <c r="E19">
+        <v>76</v>
+      </c>
+      <c r="F19" s="15">
+        <f t="shared" si="0"/>
+        <v>56.666666666666664</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" t="s">
+        <v>208</v>
+      </c>
+      <c r="C20">
+        <v>65</v>
+      </c>
+      <c r="D20">
+        <v>33</v>
+      </c>
+      <c r="E20">
+        <v>65</v>
+      </c>
+      <c r="F20" s="15">
+        <f t="shared" si="0"/>
+        <v>54.333333333333336</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" t="s">
+        <v>128</v>
+      </c>
+      <c r="C21">
+        <v>33</v>
+      </c>
+      <c r="D21">
+        <v>45</v>
+      </c>
+      <c r="E21">
+        <v>54</v>
+      </c>
+      <c r="F21" s="15">
+        <f t="shared" si="0"/>
+        <v>44</v>
       </c>
     </row>
   </sheetData>
@@ -2942,272 +3244,272 @@
   </cols>
   <sheetData>
     <row r="2" spans="1:3" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="20" t="s">
+      <c r="A2" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="C2" s="17" t="s">
         <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="18.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="B3" s="22">
+      <c r="B3" s="19">
         <v>45292</v>
       </c>
-      <c r="C3" s="21">
+      <c r="C3" s="18">
         <v>12000</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="18.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="23" t="s">
+      <c r="A4" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="B4" s="24">
+      <c r="B4" s="21">
         <v>45294</v>
       </c>
-      <c r="C4" s="23">
+      <c r="C4" s="20">
         <v>25000</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="18.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="21" t="s">
+      <c r="A5" s="18" t="s">
         <v>69</v>
       </c>
-      <c r="B5" s="22">
+      <c r="B5" s="19">
         <v>45296</v>
       </c>
-      <c r="C5" s="21">
+      <c r="C5" s="18">
         <v>8000</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="18.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="23" t="s">
+      <c r="A6" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="B6" s="24">
+      <c r="B6" s="21">
         <v>45299</v>
       </c>
-      <c r="C6" s="23">
+      <c r="C6" s="20">
         <v>32000</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="18.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="21" t="s">
+      <c r="A7" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="B7" s="22">
+      <c r="B7" s="19">
         <v>45301</v>
       </c>
-      <c r="C7" s="21">
+      <c r="C7" s="18">
         <v>15000</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="18.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="21" t="s">
+      <c r="A8" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="B8" s="25">
+      <c r="B8" s="22">
         <v>45300</v>
       </c>
-      <c r="C8" s="23">
+      <c r="C8" s="20">
         <v>30000</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="18.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="23" t="s">
+      <c r="A9" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="B9" s="25">
+      <c r="B9" s="22">
         <v>45298</v>
       </c>
-      <c r="C9" s="26">
+      <c r="C9" s="23">
         <v>40000</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="18.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="21" t="s">
+      <c r="A10" s="18" t="s">
         <v>74</v>
       </c>
-      <c r="B10" s="25">
+      <c r="B10" s="22">
         <v>45295</v>
       </c>
-      <c r="C10" s="27">
+      <c r="C10" s="24">
         <v>33000</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="18.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="23" t="s">
+      <c r="A11" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="B11" s="25">
+      <c r="B11" s="22">
         <v>45297</v>
       </c>
-      <c r="C11" s="27">
+      <c r="C11" s="24">
         <v>23000</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="18.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="21" t="s">
+      <c r="A12" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="B12" s="25">
+      <c r="B12" s="22">
         <v>45306</v>
       </c>
-      <c r="C12" s="27">
+      <c r="C12" s="24">
         <v>37000</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="18.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="21" t="s">
+      <c r="A13" s="18" t="s">
         <v>77</v>
       </c>
-      <c r="B13" s="25">
+      <c r="B13" s="22">
         <v>45303</v>
       </c>
-      <c r="C13" s="27">
+      <c r="C13" s="24">
         <v>25000</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="18.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="23" t="s">
+      <c r="A14" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="B14" s="25">
+      <c r="B14" s="22">
         <v>45302</v>
       </c>
-      <c r="C14" s="27">
+      <c r="C14" s="24">
         <v>38000</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="18.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="21" t="s">
+      <c r="A15" s="18" t="s">
         <v>79</v>
       </c>
-      <c r="B15" s="25">
+      <c r="B15" s="22">
         <v>45308</v>
       </c>
-      <c r="C15" s="27">
+      <c r="C15" s="24">
         <v>31000</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="18.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="23" t="s">
+      <c r="A16" s="20" t="s">
         <v>80</v>
       </c>
-      <c r="B16" s="25">
+      <c r="B16" s="22">
         <v>45304</v>
       </c>
-      <c r="C16" s="27">
+      <c r="C16" s="24">
         <v>23000</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="18.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="21" t="s">
+      <c r="A17" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="B17" s="25">
+      <c r="B17" s="22">
         <v>45307</v>
       </c>
-      <c r="C17" s="27">
+      <c r="C17" s="24">
         <v>26000</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="18.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="21" t="s">
+      <c r="A18" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="B18" s="25">
+      <c r="B18" s="22">
         <v>45305</v>
       </c>
-      <c r="C18" s="27">
+      <c r="C18" s="24">
         <v>34000</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="18.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="23" t="s">
+      <c r="A19" s="20" t="s">
         <v>83</v>
       </c>
-      <c r="B19" s="25">
+      <c r="B19" s="22">
         <v>45309</v>
       </c>
-      <c r="C19" s="27">
+      <c r="C19" s="24">
         <v>28000</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="18.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="21" t="s">
+      <c r="A20" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="B20" s="25">
+      <c r="B20" s="22">
         <v>45310</v>
       </c>
-      <c r="C20" s="27">
+      <c r="C20" s="24">
         <v>32000</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="18.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="23" t="s">
+      <c r="A21" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="B21" s="25">
+      <c r="B21" s="22">
         <v>45296</v>
       </c>
-      <c r="C21" s="27">
+      <c r="C21" s="24">
         <v>37000</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="18.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="21" t="s">
+      <c r="A22" s="18" t="s">
         <v>86</v>
       </c>
-      <c r="B22" s="25">
+      <c r="B22" s="22">
         <v>45297</v>
       </c>
-      <c r="C22" s="27">
+      <c r="C22" s="24">
         <v>12000</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="18.75" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="21" t="s">
+      <c r="A23" s="18" t="s">
         <v>87</v>
       </c>
-      <c r="B23" s="25"/>
-      <c r="C23" s="27">
+      <c r="B23" s="22"/>
+      <c r="C23" s="24">
         <f>SUM(C3:C22)</f>
         <v>541000</v>
       </c>
     </row>
     <row r="24" spans="1:3" ht="18" thickTop="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="28" t="s">
+      <c r="A24" s="25" t="s">
         <v>88</v>
       </c>
-      <c r="B24" s="29"/>
-      <c r="C24" s="30">
+      <c r="B24" s="26"/>
+      <c r="C24" s="27">
         <f>AVERAGE(C3:C22)</f>
         <v>27050</v>
       </c>
     </row>
     <row r="25" spans="1:3" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A25" s="28" t="s">
+      <c r="A25" s="25" t="s">
         <v>89</v>
       </c>
-      <c r="B25" s="29"/>
-      <c r="C25" s="30">
+      <c r="B25" s="26"/>
+      <c r="C25" s="27">
         <f>MAX(C3:C22)</f>
         <v>40000</v>
       </c>
     </row>
     <row r="26" spans="1:3" ht="17.25" x14ac:dyDescent="0.25">
-      <c r="A26" s="28" t="s">
+      <c r="A26" s="25" t="s">
         <v>90</v>
       </c>
-      <c r="B26" s="29"/>
-      <c r="C26" s="30">
+      <c r="B26" s="26"/>
+      <c r="C26" s="27">
         <f>MIN(C3:C22)</f>
         <v>8000</v>
       </c>
@@ -3514,48 +3816,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="35.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>116</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>118</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>119</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>120</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>142</v>
       </c>
     </row>
     <row r="2" spans="1:8" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="3" t="s">
+      <c r="A2" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="C2" s="3" t="s">
+      <c r="B2" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="D2" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="F2" s="3" t="s">
+      <c r="D2" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>123</v>
       </c>
       <c r="G2">
@@ -3568,22 +3870,22 @@
       </c>
     </row>
     <row r="3" spans="1:8" ht="35.25" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="E3" s="4" t="s">
+      <c r="B3" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="3" t="s">
         <v>123</v>
       </c>
       <c r="G3">
@@ -3596,22 +3898,22 @@
       </c>
     </row>
     <row r="4" spans="1:8" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C4" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="D4" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="F4" s="3" t="s">
+      <c r="C4" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>123</v>
       </c>
       <c r="G4">
@@ -3624,22 +3926,22 @@
       </c>
     </row>
     <row r="5" spans="1:8" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="4" t="s">
+      <c r="A5" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="C5" s="4" t="s">
+      <c r="B5" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C5" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="E5" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="F5" s="4" t="s">
+      <c r="E5" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>100</v>
       </c>
       <c r="G5">
@@ -3652,22 +3954,22 @@
       </c>
     </row>
     <row r="6" spans="1:8" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="C6" s="3" t="s">
+      <c r="B6" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="D6" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="F6" s="3" t="s">
+      <c r="D6" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>123</v>
       </c>
       <c r="G6">
@@ -3680,22 +3982,22 @@
       </c>
     </row>
     <row r="7" spans="1:8" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="E7" s="4" t="s">
+      <c r="B7" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="E7" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="3" t="s">
         <v>123</v>
       </c>
       <c r="G7">
@@ -3708,22 +4010,22 @@
       </c>
     </row>
     <row r="8" spans="1:8" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C8" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="F8" s="3" t="s">
+      <c r="C8" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="F8" s="2" t="s">
         <v>123</v>
       </c>
       <c r="G8">
@@ -3736,22 +4038,22 @@
       </c>
     </row>
     <row r="9" spans="1:8" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="4" t="s">
+      <c r="A9" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="C9" s="4" t="s">
+      <c r="B9" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C9" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="E9" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="F9" s="4" t="s">
+      <c r="E9" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>100</v>
       </c>
       <c r="G9">
@@ -3764,22 +4066,22 @@
       </c>
     </row>
     <row r="10" spans="1:8" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="C10" s="3" t="s">
+      <c r="B10" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="D10" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="F10" s="3" t="s">
+      <c r="D10" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="F10" s="2" t="s">
         <v>123</v>
       </c>
       <c r="G10">
@@ -3792,22 +4094,22 @@
       </c>
     </row>
     <row r="11" spans="1:8" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="4" t="s">
+      <c r="A11" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="B11" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="E11" s="4" t="s">
+      <c r="B11" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="E11" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="F11" s="4" t="s">
+      <c r="F11" s="3" t="s">
         <v>123</v>
       </c>
       <c r="G11">
@@ -3820,22 +4122,22 @@
       </c>
     </row>
     <row r="12" spans="1:8" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="F12" s="3" t="s">
+      <c r="C12" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="F12" s="2" t="s">
         <v>123</v>
       </c>
       <c r="G12">
@@ -3848,22 +4150,22 @@
       </c>
     </row>
     <row r="13" spans="1:8" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="4" t="s">
+      <c r="A13" s="3" t="s">
         <v>133</v>
       </c>
-      <c r="B13" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="C13" s="4" t="s">
+      <c r="B13" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C13" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="E13" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="F13" s="4" t="s">
+      <c r="E13" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>100</v>
       </c>
       <c r="G13">
@@ -3876,22 +4178,22 @@
       </c>
     </row>
     <row r="14" spans="1:8" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="C14" s="3" t="s">
+      <c r="B14" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="F14" s="3" t="s">
+      <c r="D14" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="F14" s="2" t="s">
         <v>123</v>
       </c>
       <c r="G14">
@@ -3904,22 +4206,22 @@
       </c>
     </row>
     <row r="15" spans="1:8" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="4" t="s">
+      <c r="A15" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="B15" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="E15" s="4" t="s">
+      <c r="B15" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="E15" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="F15" s="4" t="s">
+      <c r="F15" s="3" t="s">
         <v>123</v>
       </c>
       <c r="G15">
@@ -3932,22 +4234,22 @@
       </c>
     </row>
     <row r="16" spans="1:8" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C16" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="F16" s="3" t="s">
+      <c r="C16" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="F16" s="2" t="s">
         <v>123</v>
       </c>
       <c r="G16">
@@ -3960,22 +4262,22 @@
       </c>
     </row>
     <row r="17" spans="1:8" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="4" t="s">
+      <c r="A17" s="3" t="s">
         <v>137</v>
       </c>
-      <c r="B17" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="C17" s="4" t="s">
+      <c r="B17" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C17" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="E17" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="F17" s="4" t="s">
+      <c r="E17" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="F17" s="3" t="s">
         <v>100</v>
       </c>
       <c r="G17">
@@ -3988,22 +4290,22 @@
       </c>
     </row>
     <row r="18" spans="1:8" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="2" t="s">
         <v>138</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="C18" s="3" t="s">
+      <c r="B18" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="C18" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="F18" s="3" t="s">
+      <c r="D18" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="F18" s="2" t="s">
         <v>123</v>
       </c>
       <c r="G18">
@@ -4016,22 +4318,22 @@
       </c>
     </row>
     <row r="19" spans="1:8" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="4" t="s">
+      <c r="A19" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="B19" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="E19" s="4" t="s">
+      <c r="B19" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D19" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="E19" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="F19" s="3" t="s">
         <v>123</v>
       </c>
       <c r="G19">
@@ -4044,22 +4346,22 @@
       </c>
     </row>
     <row r="20" spans="1:8" ht="18" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C20" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>123</v>
-      </c>
-      <c r="F20" s="3" t="s">
+      <c r="C20" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="F20" s="2" t="s">
         <v>123</v>
       </c>
       <c r="G20">
@@ -4098,7 +4400,7 @@
       <c r="A2" t="s">
         <v>144</v>
       </c>
-      <c r="B2" s="31">
+      <c r="B2" s="28">
         <v>4500</v>
       </c>
     </row>
@@ -4466,11 +4768,11 @@
     </row>
   </sheetData>
   <conditionalFormatting sqref="B2:B21">
-    <cfRule type="cellIs" dxfId="9" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="6" priority="1" operator="lessThan">
+      <formula>5000</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="5" priority="2" operator="greaterThan">
       <formula>20000</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="10" priority="1" operator="lessThan">
-      <formula>5000</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
